--- a/data/gravel/Sage Storm King GP 2025.xlsx
+++ b/data/gravel/Sage Storm King GP 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04DF7D9B-FECB-EB47-8727-23EF352847EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D481021B-4886-3A4A-994F-72A8790B593D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{ABFFBBBD-2C2A-DA41-8959-3BF392F3D8AC}"/>
+    <workbookView xWindow="0" yWindow="1320" windowWidth="28800" windowHeight="13300" xr2:uid="{ABFFBBBD-2C2A-DA41-8959-3BF392F3D8AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sage Storm King GP 2025" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="204">
   <si>
     <t>model</t>
   </si>
@@ -128,12 +128,6 @@
     <t>material</t>
   </si>
   <si>
-    <t>frame weight</t>
-  </si>
-  <si>
-    <t>UDH</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -533,17 +527,134 @@
     <t>seat_tube_angle_actual</t>
   </si>
   <si>
-    <t>a10:j34</t>
-  </si>
-  <si>
     <t>2 cm shorter than 90 mm stem spec for earlier models</t>
+  </si>
+  <si>
+    <t>udh</t>
+  </si>
+  <si>
+    <t>dropout</t>
+  </si>
+  <si>
+    <t>650B tire max</t>
+  </si>
+  <si>
+    <t>suspension corrected</t>
+  </si>
+  <si>
+    <t>rear axle</t>
+  </si>
+  <si>
+    <t>front axle</t>
+  </si>
+  <si>
+    <t>q-factor</t>
+  </si>
+  <si>
+    <t>seatpost diameter</t>
+  </si>
+  <si>
+    <t>routing shifter</t>
+  </si>
+  <si>
+    <t>routing dropper</t>
+  </si>
+  <si>
+    <t>routing dynamo</t>
+  </si>
+  <si>
+    <t>front derailleur</t>
+  </si>
+  <si>
+    <t>chainring 1</t>
+  </si>
+  <si>
+    <t>chainring 2</t>
+  </si>
+  <si>
+    <t>bottom bracket</t>
+  </si>
+  <si>
+    <t>mounts inner</t>
+  </si>
+  <si>
+    <t>mounts under</t>
+  </si>
+  <si>
+    <t>mounts top</t>
+  </si>
+  <si>
+    <t>mounts fork</t>
+  </si>
+  <si>
+    <t>mounts fender rear</t>
+  </si>
+  <si>
+    <t>mounts fender front</t>
+  </si>
+  <si>
+    <t>mounts rack</t>
+  </si>
+  <si>
+    <t>rotor max front</t>
+  </si>
+  <si>
+    <t>rotor max rear</t>
+  </si>
+  <si>
+    <t>frameset</t>
+  </si>
+  <si>
+    <t>base build</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>a10:j35</t>
+  </si>
+  <si>
+    <t>49/31</t>
+  </si>
+  <si>
+    <t>internal</t>
+  </si>
+  <si>
+    <t>T47</t>
+  </si>
+  <si>
+    <t>us</t>
+  </si>
+  <si>
+    <t>frame_weight</t>
+  </si>
+  <si>
+    <t>fork suspension</t>
+  </si>
+  <si>
+    <t>stem suspension</t>
+  </si>
+  <si>
+    <t>rear suspension</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>internal storage</t>
+  </si>
+  <si>
+    <t>700c width max</t>
+  </si>
+  <si>
+    <t>ISO ASTM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -579,6 +690,12 @@
       <color rgb="FF000000"/>
       <name val="Futura Medium"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -600,13 +717,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -630,13 +751,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -678,13 +799,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -726,7 +847,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -769,7 +890,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -812,7 +933,7 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -855,7 +976,7 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -898,7 +1019,7 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -941,7 +1062,7 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>88900</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="317500"/>
@@ -984,7 +1105,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="317500"/>
@@ -1027,7 +1148,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="317500"/>
@@ -1070,7 +1191,7 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="317500"/>
@@ -1113,7 +1234,7 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="317500"/>
@@ -1156,7 +1277,7 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="317500"/>
@@ -1199,7 +1320,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1242,7 +1363,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1285,7 +1406,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1328,7 +1449,7 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1371,7 +1492,7 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1414,7 +1535,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1457,7 +1578,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1500,7 +1621,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1543,7 +1664,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1586,7 +1707,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1629,7 +1750,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1672,7 +1793,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1715,7 +1836,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1801,7 +1922,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1844,7 +1965,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1887,7 +2008,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1930,7 +2051,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -1973,7 +2094,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2016,7 +2137,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2059,7 +2180,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2102,7 +2223,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2188,7 +2309,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2231,7 +2352,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2274,7 +2395,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2317,7 +2438,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2360,7 +2481,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2403,7 +2524,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2446,7 +2567,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2489,7 +2610,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2532,7 +2653,7 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="304800" cy="304800"/>
@@ -2891,32 +3012,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3856DE37-3828-6849-A98A-EC05E320BDEE}">
-  <dimension ref="A1:AD37"/>
+  <dimension ref="A1:AH38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.6640625" style="1" customWidth="1"/>
     <col min="3" max="10" width="13.5" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="10.83203125" style="1"/>
+    <col min="11" max="13" width="10.83203125" style="1"/>
+    <col min="14" max="14" width="13.5" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2924,7 +3047,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2932,49 +3055,206 @@
         <v>45849</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:34" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>33</v>
+      <c r="B6" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="S6" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="T6" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="U6" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="V6" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="W6" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="X6" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y6" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z6" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA6" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB6" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="AC6" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="AD6" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="AE6" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="AF6" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="AG6" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="AH6" s="6" t="s">
+        <v>201</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>57</v>
+      </c>
+      <c r="F7" s="1">
+        <v>40</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="J7" s="1">
+        <v>142</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+      <c r="M7" s="1">
+        <v>31.6</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="R7" s="1">
+        <v>44</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="U7" s="1">
+        <v>2</v>
+      </c>
+      <c r="V7" s="1">
+        <v>1</v>
+      </c>
+      <c r="W7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>5700</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>8628.33</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>200</v>
+      </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>32</v>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>191</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1" t="str">
         <f>M10</f>
@@ -3009,31 +3289,31 @@
         <v>62 CM</v>
       </c>
       <c r="M10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="P10" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="O10" s="1" t="s">
+      <c r="Q10" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="P10" s="1" t="s">
+      <c r="R10" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="S10" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="R10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="T10" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
@@ -3074,7 +3354,7 @@
         <v>575</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M11" s="1">
         <v>45</v>
@@ -3101,34 +3381,34 @@
         <v>57.5</v>
       </c>
       <c r="V11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="W11" s="1" t="s">
+      <c r="Y11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="X11" s="1" t="s">
+      <c r="Z11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Y11" s="1" t="s">
+      <c r="AA11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Z11" s="1" t="s">
+      <c r="AB11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AA11" s="1" t="s">
+      <c r="AC11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AB11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC11" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="AD11" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
@@ -3169,7 +3449,7 @@
         <v>630.70000000000005</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M12" s="1">
         <v>53.35</v>
@@ -3196,34 +3476,34 @@
         <v>63.07</v>
       </c>
       <c r="V12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="X12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="W12" s="1" t="s">
+      <c r="Y12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="X12" s="1" t="s">
+      <c r="Z12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="Y12" s="1" t="s">
+      <c r="AA12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="Z12" s="1" t="s">
+      <c r="AB12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AA12" s="1" t="s">
+      <c r="AC12" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AB12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC12" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AD12" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -3264,7 +3544,7 @@
         <v>71</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M13" s="1">
         <v>69.75</v>
@@ -3291,36 +3571,36 @@
         <v>71</v>
       </c>
       <c r="V13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="W13" s="1" t="s">
+      <c r="AA13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="X13" s="1" t="s">
+      <c r="AD13" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="Y13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD13" s="5" t="s">
-        <v>64</v>
-      </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B14" s="3" t="str">
         <f t="shared" si="2"/>
@@ -3359,7 +3639,7 @@
         <v>71.5</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M14" s="1">
         <v>73.5</v>
@@ -3386,34 +3666,34 @@
         <v>71.5</v>
       </c>
       <c r="V14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="W14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="X14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y14" s="1" t="s">
+      <c r="AA14" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Z14" s="1" t="s">
+      <c r="AB14" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AA14" s="1" t="s">
+      <c r="AC14" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB14" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC14" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="AD14" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
@@ -3454,7 +3734,7 @@
         <v>74.59</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="M15" s="1">
         <v>76.87</v>
@@ -3481,34 +3761,34 @@
         <v>74.59</v>
       </c>
       <c r="V15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y15" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="W15" s="1" t="s">
+      <c r="Z15" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="X15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y15" s="1" t="s">
+      <c r="AA15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Z15" s="1" t="s">
+      <c r="AB15" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="AA15" s="1" t="s">
+      <c r="AC15" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AB15" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AC15" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="AD15" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -3549,7 +3829,7 @@
         <v>876</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M16" s="1">
         <v>75.7</v>
@@ -3576,31 +3856,31 @@
         <v>87.6</v>
       </c>
       <c r="V16" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="X16" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="W16" s="1" t="s">
+      <c r="Y16" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="X16" s="1" t="s">
+      <c r="Z16" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="Y16" s="1" t="s">
+      <c r="AA16" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="Z16" s="1" t="s">
+      <c r="AB16" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="AA16" s="1" t="s">
+      <c r="AC16" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AB16" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC16" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="AD16" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.3">
@@ -3644,7 +3924,7 @@
         <v>195</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M17" s="1">
         <v>9</v>
@@ -3671,31 +3951,31 @@
         <v>19.5</v>
       </c>
       <c r="V17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="X17" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="W17" s="1" t="s">
+      <c r="Y17" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="X17" s="1" t="s">
+      <c r="Z17" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="Y17" s="1" t="s">
+      <c r="AA17" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="Z17" s="1" t="s">
+      <c r="AB17" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="AA17" s="1" t="s">
+      <c r="AC17" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="AB17" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC17" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="AD17" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.3">
@@ -3739,7 +4019,7 @@
         <v>1110.4000000000001</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M18" s="1">
         <v>103.74</v>
@@ -3766,31 +4046,31 @@
         <v>111.04</v>
       </c>
       <c r="V18" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="X18" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="W18" s="1" t="s">
+      <c r="Y18" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="X18" s="1" t="s">
+      <c r="Z18" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="Y18" s="1" t="s">
+      <c r="AA18" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="Z18" s="1" t="s">
+      <c r="AB18" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AA18" s="1" t="s">
+      <c r="AC18" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AB18" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC18" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="AD18" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.3">
@@ -3834,7 +4114,7 @@
         <v>691.9</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M19" s="1">
         <v>62.44</v>
@@ -3861,31 +4141,31 @@
         <v>69.19</v>
       </c>
       <c r="V19" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="X19" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="W19" s="1" t="s">
+      <c r="Y19" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="X19" s="1" t="s">
+      <c r="Z19" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="Y19" s="1" t="s">
+      <c r="AA19" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="Z19" s="1" t="s">
+      <c r="AB19" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="AA19" s="1" t="s">
+      <c r="AC19" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AB19" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC19" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="AD19" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.3">
@@ -3929,7 +4209,7 @@
         <v>427</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M20" s="1">
         <v>42.3</v>
@@ -3956,31 +4236,31 @@
         <v>42.7</v>
       </c>
       <c r="V20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z20" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="W20" s="1" t="s">
+      <c r="AA20" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC20" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X20" s="1" t="s">
+      <c r="AD20" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="Y20" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z20" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA20" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AB20" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AC20" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="AD20" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.3">
@@ -4024,7 +4304,7 @@
         <v>67</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M21" s="1">
         <v>71</v>
@@ -4051,31 +4331,31 @@
         <v>67</v>
       </c>
       <c r="V21" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y21" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="W21" s="1" t="s">
+      <c r="Z21" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="X21" s="1" t="s">
+      <c r="AA21" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="Y21" s="1" t="s">
+      <c r="AB21" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="Z21" s="1" t="s">
+      <c r="AC21" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="AA21" s="1" t="s">
+      <c r="AD21" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="AB21" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC21" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AD21" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.3">
@@ -4119,7 +4399,7 @@
         <v>71.739999999999995</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M22" s="1">
         <v>77.709999999999994</v>
@@ -4146,31 +4426,31 @@
         <v>71.739999999999995</v>
       </c>
       <c r="V22" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="X22" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="W22" s="1" t="s">
+      <c r="Y22" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="X22" s="1" t="s">
+      <c r="Z22" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="Y22" s="1" t="s">
+      <c r="AA22" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC22" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="Z22" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="AA22" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="AB22" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="AC22" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="AD22" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.3">
@@ -4214,7 +4494,7 @@
         <v>647</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M23" s="1">
         <v>54.68</v>
@@ -4241,31 +4521,31 @@
         <v>64.7</v>
       </c>
       <c r="V23" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="X23" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="W23" s="1" t="s">
+      <c r="Y23" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="X23" s="1" t="s">
+      <c r="Z23" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="Y23" s="1" t="s">
+      <c r="AA23" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="Z23" s="1" t="s">
+      <c r="AB23" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="AA23" s="1" t="s">
+      <c r="AC23" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="AB23" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC23" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="AD23" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.3">
@@ -4309,7 +4589,7 @@
         <v>435</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M24" s="1">
         <v>39.04</v>
@@ -4336,31 +4616,31 @@
         <v>43.5</v>
       </c>
       <c r="V24" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="X24" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="W24" s="1" t="s">
+      <c r="Y24" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="X24" s="1" t="s">
+      <c r="Z24" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="Y24" s="1" t="s">
+      <c r="AA24" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="Z24" s="1" t="s">
+      <c r="AB24" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="AA24" s="1" t="s">
+      <c r="AC24" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="AB24" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="AC24" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="AD24" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.3">
@@ -4404,7 +4684,7 @@
         <v>435</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M25" s="1">
         <v>43.5</v>
@@ -4431,31 +4711,31 @@
         <v>43.5</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AA25" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AB25" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AC25" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AD25" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.3">
@@ -4499,7 +4779,7 @@
         <v>51</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M26" s="1">
         <v>51</v>
@@ -4526,252 +4806,258 @@
         <v>51</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AA26" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AC26" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AD26" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>19</v>
+        <v>196</v>
       </c>
       <c r="B27" s="3"/>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="1">
-        <v>50</v>
-      </c>
-      <c r="D28" s="1">
-        <v>60</v>
-      </c>
-      <c r="E28" s="1">
-        <v>60</v>
-      </c>
-      <c r="F28" s="1">
-        <v>70</v>
-      </c>
-      <c r="G28" s="1">
-        <v>70</v>
-      </c>
-      <c r="H28" s="1">
-        <v>80</v>
-      </c>
-      <c r="I28" s="1">
-        <v>90</v>
-      </c>
-      <c r="J28" s="1">
-        <v>100</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>166</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B28" s="3"/>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="C29" s="1">
+        <v>50</v>
+      </c>
+      <c r="D29" s="1">
+        <v>60</v>
+      </c>
+      <c r="E29" s="1">
+        <v>60</v>
+      </c>
+      <c r="F29" s="1">
+        <v>70</v>
+      </c>
+      <c r="G29" s="1">
+        <v>70</v>
+      </c>
+      <c r="H29" s="1">
+        <v>80</v>
+      </c>
+      <c r="I29" s="1">
+        <v>90</v>
+      </c>
+      <c r="J29" s="1">
+        <v>100</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="1">
-        <v>700</v>
-      </c>
-      <c r="D30" s="1">
-        <v>700</v>
-      </c>
-      <c r="E30" s="1">
-        <v>700</v>
-      </c>
-      <c r="F30" s="1">
-        <v>700</v>
-      </c>
-      <c r="G30" s="1">
-        <v>700</v>
-      </c>
-      <c r="H30" s="1">
-        <v>700</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C31" s="1">
-        <v>40</v>
+        <v>700</v>
       </c>
       <c r="D31" s="1">
-        <v>40</v>
+        <v>700</v>
       </c>
       <c r="E31" s="1">
-        <v>40</v>
+        <v>700</v>
       </c>
       <c r="F31" s="1">
-        <v>40</v>
+        <v>700</v>
       </c>
       <c r="G31" s="1">
-        <v>40</v>
+        <v>700</v>
       </c>
       <c r="H31" s="1">
-        <v>40</v>
+        <v>700</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C32" s="1">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D32" s="1">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E32" s="1">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="F32" s="1">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="G32" s="1">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="H32" s="1">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C33" s="1">
-        <v>150</v>
+        <v>57</v>
       </c>
       <c r="D33" s="1">
-        <v>160</v>
+        <v>57</v>
       </c>
       <c r="E33" s="1">
-        <v>168</v>
+        <v>57</v>
       </c>
       <c r="F33" s="1">
-        <v>176</v>
+        <v>57</v>
       </c>
       <c r="G33" s="1">
-        <v>184</v>
+        <v>57</v>
       </c>
       <c r="H33" s="1">
-        <v>192</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C34" s="1">
+        <v>150</v>
+      </c>
+      <c r="D34" s="1">
         <v>160</v>
       </c>
-      <c r="D34" s="1">
+      <c r="E34" s="1">
         <v>168</v>
       </c>
-      <c r="E34" s="1">
+      <c r="F34" s="1">
         <v>176</v>
       </c>
-      <c r="F34" s="1">
+      <c r="G34" s="1">
         <v>184</v>
       </c>
-      <c r="G34" s="1">
+      <c r="H34" s="1">
         <v>192</v>
-      </c>
-      <c r="H34" s="1">
-        <v>200</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C35" s="1">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="D35" s="1">
-        <v>63.5</v>
+        <v>168</v>
       </c>
       <c r="E35" s="1">
-        <v>67.5</v>
+        <v>176</v>
       </c>
       <c r="F35" s="1">
-        <v>70</v>
+        <v>184</v>
       </c>
       <c r="G35" s="1">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="H35" s="1">
-        <v>73.5</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C36" s="1">
+        <v>60</v>
+      </c>
+      <c r="D36" s="1">
         <v>63.5</v>
       </c>
-      <c r="D36" s="1">
+      <c r="E36" s="1">
         <v>67.5</v>
       </c>
-      <c r="E36" s="1">
+      <c r="F36" s="1">
         <v>70</v>
       </c>
-      <c r="F36" s="1">
+      <c r="G36" s="1">
         <v>72</v>
       </c>
-      <c r="G36" s="1">
+      <c r="H36" s="1">
         <v>73.5</v>
-      </c>
-      <c r="H36" s="1">
-        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="1">
+        <v>63.5</v>
+      </c>
+      <c r="D37" s="1">
+        <v>67.5</v>
+      </c>
+      <c r="E37" s="1">
+        <v>70</v>
+      </c>
+      <c r="F37" s="1">
+        <v>72</v>
+      </c>
+      <c r="G37" s="1">
+        <v>73.5</v>
+      </c>
+      <c r="H37" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B38" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="E38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="H38" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Sage Storm King GP 2025.xlsx
+++ b/data/gravel/Sage Storm King GP 2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EABCCA5E-DBE0-9E43-AA0C-92D622D8D817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2EEC46C-3904-AB4A-96F9-F9CFA7606DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="26860" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="124">
   <si>
     <t>brand</t>
   </si>
@@ -374,6 +374,24 @@
   </si>
   <si>
     <t>us</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -705,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1454,248 +1472,272 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="B37" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>73</v>
+        <v>67</v>
+      </c>
+      <c r="B40" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>77</v>
-      </c>
-      <c r="B43" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B45" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B46" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>80</v>
+      </c>
+      <c r="B48" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B49" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>90</v>
-      </c>
-      <c r="B51" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>94</v>
+        <v>89</v>
+      </c>
+      <c r="B53" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>95</v>
+        <v>90</v>
+      </c>
+      <c r="B54" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>96</v>
+        <v>92</v>
+      </c>
+      <c r="B55" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>97</v>
-      </c>
-      <c r="B56" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>99</v>
-      </c>
-      <c r="B57" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B59" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B60" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>104</v>
-      </c>
-      <c r="B61" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B62" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>107</v>
+        <v>102</v>
+      </c>
+      <c r="B63" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>108</v>
+        <v>104</v>
+      </c>
+      <c r="B64" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>109</v>
+        <v>106</v>
+      </c>
+      <c r="B65" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>111</v>
-      </c>
-      <c r="B67" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>113</v>
-      </c>
-      <c r="B68" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>111</v>
+      </c>
+      <c r="B70" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>113</v>
+      </c>
+      <c r="B71" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>116</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B73" t="s">
         <v>117</v>
       </c>
     </row>

--- a/data/gravel/Sage Storm King GP 2025.xlsx
+++ b/data/gravel/Sage Storm King GP 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2EEC46C-3904-AB4A-96F9-F9CFA7606DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5982AEAF-F4BD-D74C-AE44-3FD8F2931BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="26860" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="124">
   <si>
     <t>brand</t>
   </si>
@@ -391,18 +391,24 @@
     <t>fork</t>
   </si>
   <si>
-    <t>rigid</t>
+    <t>suspension</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Futura"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -425,8 +431,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1490,7 +1497,7 @@
       <c r="A38" t="s">
         <v>122</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1543,24 +1550,18 @@
       <c r="A45" t="s">
         <v>76</v>
       </c>
-      <c r="B45" t="s">
-        <v>68</v>
+      <c r="B45">
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>77</v>
       </c>
-      <c r="B46" t="s">
-        <v>78</v>
-      </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>79</v>
-      </c>
-      <c r="B47" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Sage Storm King GP 2025.xlsx
+++ b/data/gravel/Sage Storm King GP 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5982AEAF-F4BD-D74C-AE44-3FD8F2931BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2F6DD0-EE00-AD4A-B640-E949CF323D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="26860" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -392,6 +392,9 @@
   </si>
   <si>
     <t>suspension</t>
+  </si>
+  <si>
+    <t>https://sagetitanium.wpenginepowered.com/wp-content/uploads/2024/05/GP-Red-Profile-Website-Edit.jpg</t>
   </si>
 </sst>
 </file>
@@ -776,6 +779,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>124</v>
+      </c>
+    </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>

--- a/data/gravel/Sage Storm King GP 2025.xlsx
+++ b/data/gravel/Sage Storm King GP 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2F6DD0-EE00-AD4A-B640-E949CF323D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76C15CB-C75B-5349-B1A1-02C81385C71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="26860" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17120" yWindow="500" windowWidth="26860" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -301,9 +301,6 @@
     <t>max_chainring_2x</t>
   </si>
   <si>
-    <t>49/31</t>
-  </si>
-  <si>
     <t>rotor_max_front</t>
   </si>
   <si>
@@ -373,9 +370,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -395,6 +389,15 @@
   </si>
   <si>
     <t>https://sagetitanium.wpenginepowered.com/wp-content/uploads/2024/05/GP-Red-Profile-Website-Edit.jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Beaverton, Oregon, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -733,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -781,7 +784,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1487,26 +1490,26 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B36" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B37" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -1629,49 +1632,49 @@
       <c r="A55" t="s">
         <v>92</v>
       </c>
-      <c r="B55" t="s">
-        <v>93</v>
+      <c r="B55">
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>96</v>
+      </c>
+      <c r="B59" t="s">
         <v>97</v>
-      </c>
-      <c r="B59" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B62" t="s">
         <v>78</v>
@@ -1679,75 +1682,83 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>101</v>
+      </c>
+      <c r="B63" t="s">
         <v>102</v>
-      </c>
-      <c r="B63" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>103</v>
+      </c>
+      <c r="B64" t="s">
         <v>104</v>
-      </c>
-      <c r="B64" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B65" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>110</v>
+      </c>
+      <c r="B70" t="s">
         <v>111</v>
-      </c>
-      <c r="B70" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>112</v>
+      </c>
+      <c r="B71" t="s">
         <v>113</v>
-      </c>
-      <c r="B71" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>116</v>
-      </c>
-      <c r="B73" t="s">
-        <v>117</v>
+        <v>115</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>123</v>
+      </c>
+      <c r="B74" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Sage Storm King GP 2025.xlsx
+++ b/data/gravel/Sage Storm King GP 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76C15CB-C75B-5349-B1A1-02C81385C71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABB1EC5-F961-1B46-81A3-4F668660229A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17120" yWindow="500" windowWidth="26860" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="132">
   <si>
     <t>brand</t>
   </si>
@@ -398,6 +398,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -736,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1593,171 +1611,201 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>84</v>
-      </c>
-      <c r="B50" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>87</v>
-      </c>
-      <c r="B52" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>89</v>
-      </c>
-      <c r="B53" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>90</v>
-      </c>
-      <c r="B54" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>92</v>
-      </c>
-      <c r="B55">
-        <v>49</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>93</v>
+        <v>84</v>
+      </c>
+      <c r="B56" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>95</v>
+        <v>87</v>
+      </c>
+      <c r="B58" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B59" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B60" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>99</v>
+        <v>92</v>
+      </c>
+      <c r="B61">
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>100</v>
-      </c>
-      <c r="B62" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>101</v>
-      </c>
-      <c r="B63" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>103</v>
-      </c>
-      <c r="B64" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B65" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>106</v>
+        <v>98</v>
+      </c>
+      <c r="B66" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>108</v>
+        <v>100</v>
+      </c>
+      <c r="B68" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>109</v>
+        <v>101</v>
+      </c>
+      <c r="B69" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B70" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B71" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>115</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>110</v>
+      </c>
+      <c r="B76" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>112</v>
+      </c>
+      <c r="B77" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>115</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>123</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>124</v>
       </c>
     </row>
